--- a/docs/requerimiento-5/I.S.F.D. y T. N° 93_ Inscripción a Carreras 2021 (solo 1).xlsx
+++ b/docs/requerimiento-5/I.S.F.D. y T. N° 93_ Inscripción a Carreras 2021 (solo 1).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">Marca temporal</t>
   </si>
@@ -76,6 +76,18 @@
     <t xml:space="preserve">Acepta los términos y requisitos de inscripción a dicho Instituto:</t>
   </si>
   <si>
+    <t xml:space="preserve">Tipo documento</t>
+  </si>
+  <si>
+    <t>Recibo</t>
+  </si>
+  <si>
+    <t>Monto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contacto emergencia</t>
+  </si>
+  <si>
     <t>acunaagustina74@gmail.com</t>
   </si>
   <si>
@@ -114,6 +126,9 @@
   <si>
     <t>SI</t>
   </si>
+  <si>
+    <t>DNI</t>
+  </si>
 </sst>
 </file>
 
@@ -122,12 +137,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3">
-    <font>
-      <sz val="10.000000"/>
-      <color indexed="64"/>
-      <name val="Arial"/>
-    </font>
+  <fonts count="2">
     <font>
       <sz val="10.000000"/>
       <color theme="1"/>
@@ -162,12 +172,12 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="14" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" quotePrefix="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="1"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="3" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -601,16 +611,28 @@
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -675,7 +697,9 @@
     <col bestFit="1" customWidth="1" min="5" max="5" width="24"/>
     <col bestFit="1" customWidth="1" min="6" max="6" width="10.140625"/>
     <col bestFit="1" customWidth="1" min="7" max="7" width="9.42578125"/>
-    <col customWidth="1" min="8" max="24" width="21.5703125"/>
+    <col customWidth="1" min="8" max="18" width="21.5703125"/>
+    <col customWidth="1" min="19" max="19" width="33.8515625"/>
+    <col customWidth="1" min="20" max="24" width="21.5703125"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75">
@@ -733,61 +757,85 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" ht="12.75">
       <c r="A2" s="2">
         <v>44228.926002650463</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2" s="1">
         <v>43785394</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H2" s="3">
         <v>37201</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K2" s="1">
         <v>1161305919</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="O2" s="1">
         <v>1856</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
+      </c>
+      <c r="T2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2">
+        <v>321312</v>
+      </c>
+      <c r="V2">
+        <v>321312</v>
+      </c>
+      <c r="W2">
+        <v>22234144324</v>
       </c>
     </row>
     <row r="3" ht="12.75">
